--- a/data/orders.xlsx
+++ b/data/orders.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
   <si>
     <t>Order ID</t>
   </si>
@@ -155,6 +155,36 @@
   </si>
   <si>
     <t>Botanical Hydrating Mist (x3) - $96.00</t>
+  </si>
+  <si>
+    <t>ORD-645839</t>
+  </si>
+  <si>
+    <t>8/15/2026, 11:17:25 AM GMT+5</t>
+  </si>
+  <si>
+    <t>Jimmy QA</t>
+  </si>
+  <si>
+    <t>jimmy@gmail.com</t>
+  </si>
+  <si>
+    <t>434324</t>
+  </si>
+  <si>
+    <t>Swedenborgsgatan</t>
+  </si>
+  <si>
+    <t>Stockholm</t>
+  </si>
+  <si>
+    <t>11164</t>
+  </si>
+  <si>
+    <t>Rosehip Radiance Facial Serum (x1) - $48.00</t>
+  </si>
+  <si>
+    <t>$48.00</t>
   </si>
 </sst>
 </file>
@@ -547,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -708,6 +738,38 @@
       </c>
       <c r="J5" s="2" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/data/orders.xlsx
+++ b/data/orders.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="68">
   <si>
     <t>Order ID</t>
   </si>
@@ -185,6 +185,36 @@
   </si>
   <si>
     <t>$48.00</t>
+  </si>
+  <si>
+    <t>ORD-299601</t>
+  </si>
+  <si>
+    <t>8/15/2026, 5:18:19 PM GMT+5</t>
+  </si>
+  <si>
+    <t>ali ayyan</t>
+  </si>
+  <si>
+    <t>ayyan@clu.io</t>
+  </si>
+  <si>
+    <t>534534534</t>
+  </si>
+  <si>
+    <t>606 P block</t>
+  </si>
+  <si>
+    <t>lahore</t>
+  </si>
+  <si>
+    <t>3553345</t>
+  </si>
+  <si>
+    <t>Commercial Tank Cleaning Pack (x1) - $499.00</t>
+  </si>
+  <si>
+    <t>$499.00</t>
   </si>
 </sst>
 </file>
@@ -577,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -770,6 +800,38 @@
       </c>
       <c r="J6" s="2" t="s">
         <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
